--- a/Documentation/Documents/SQL Generator/Data Initial/Master.TblBankAccount.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/Master.TblBankAccount.xlsx
@@ -2338,70 +2338,7 @@
     <cellStyle name="Normal 9 2" xfId="143"/>
     <cellStyle name="Normal 9 3" xfId="144"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <fill>
         <patternFill>
@@ -41938,17 +41875,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="M4:M59">
-    <cfRule type="expression" dxfId="9" priority="6">
+    <cfRule type="expression" dxfId="2" priority="6">
       <formula>EXACT(M3, M4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M60">
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>EXACT(M59, M60)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M61:M209">
-    <cfRule type="expression" dxfId="6" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>EXACT(M60, M61)</formula>
     </cfRule>
   </conditionalFormatting>
